--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR50.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_GR__GR50.xlsx
@@ -381,59 +381,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.6935399775358946</v>
-      </c>
-      <c r="C2">
-        <v>0.1269628226537484</v>
+        <v>2.571855490523115</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D2">
-        <v>0.009728486955754628</v>
+        <v>0.04802583608335928</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.4425020111859396</v>
-      </c>
-      <c r="C3">
-        <v>0.2239469910985226</v>
+        <v>9.330912289296808</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D3">
-        <v>0.01811992807166913</v>
+        <v>0.367821917733721</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>2.24685124877906</v>
+        <v>1.094085966999758</v>
       </c>
       <c r="C4">
-        <v>0.3535263922430047</v>
+        <v>0.3027398730406212</v>
       </c>
       <c r="D4">
-        <v>0.0408234011692687</v>
+        <v>0.02783650913320033</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>3.464392068493043</v>
+          <t>A-253</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -441,33 +447,35 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.04622180507356349</v>
+        <v>0.4476872010310345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>1.094085966999758</v>
+        <v>0.9659347099536986</v>
       </c>
       <c r="C6">
-        <v>0.3027398730406212</v>
+        <v>0.2695677371875597</v>
       </c>
       <c r="D6">
-        <v>0.02783650913320033</v>
+        <v>0.03285613632048501</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>9.330912289296808</v>
+          <t>A-431</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -475,13 +483,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.367821917733721</v>
+        <v>0.6641248454212808</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -494,154 +502,146 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="D8">
-        <v>1.483267930410584</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.5750649665519596</v>
-      </c>
-      <c r="C9">
-        <v>0.2230462957064594</v>
+        <v>12.32461323195621</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D9">
-        <v>0.01562019359754237</v>
+        <v>0.9904303981282423</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>8.844692399342915</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.8817896138645508</v>
+      </c>
+      <c r="C10">
+        <v>0.196179340178133</v>
       </c>
       <c r="D10">
-        <v>0.258080254675135</v>
+        <v>0.01498150442433023</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>COLO 829</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.6935399775358946</v>
+      </c>
+      <c r="C11">
+        <v>0.1269628226537484</v>
       </c>
       <c r="D11">
-        <v>0.6641248454212808</v>
+        <v>0.009728486955754628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.9659347099536986</v>
+        <v>1.651043442088782</v>
       </c>
       <c r="C12">
-        <v>0.2695677371875597</v>
+        <v>0.2235260778818286</v>
       </c>
       <c r="D12">
-        <v>0.03285613632048501</v>
+        <v>0.0277436840039606</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13">
-        <v>2.571855490523115</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.5876457977663722</v>
+      </c>
+      <c r="C13">
+        <v>0.1991194474043793</v>
       </c>
       <c r="D13">
-        <v>0.04802583608335928</v>
+        <v>0.0186584663117371</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>G-361</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.5750649665519596</v>
       </c>
       <c r="C14">
-        <v>0.09980888242691298</v>
+        <v>0.2230462957064594</v>
       </c>
       <c r="D14">
-        <v>0.0423659765280594</v>
+        <v>0.01562019359754237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15">
-        <v>17.01097403910282</v>
+        <v>1.435263041502199</v>
       </c>
       <c r="C15">
-        <v>0.2599191751404982</v>
+        <v>0.09975869252373988</v>
       </c>
       <c r="D15">
-        <v>0.2694086767088755</v>
+        <v>0.02334934991952614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>HMY-1</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.3563202677326271</v>
       </c>
       <c r="C16">
-        <v>0.1117205701306592</v>
+        <v>0.1415222716464925</v>
       </c>
       <c r="D16">
-        <v>0.05405483045506008</v>
+        <v>0.01763198251317507</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -655,93 +655,101 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.1896826513059756</v>
+        <v>4.011365568566589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.8817896138645508</v>
+        <v>0.6754664498443901</v>
       </c>
       <c r="C18">
-        <v>0.196179340178133</v>
+        <v>0.1477995909589447</v>
       </c>
       <c r="D18">
-        <v>0.01498150442433023</v>
+        <v>0.02384760817354794</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.4542704531091089</v>
-      </c>
-      <c r="C19">
-        <v>0.1611884269058386</v>
+        <v>8.844692399342915</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D19">
-        <v>0.01305852878454457</v>
+        <v>0.258080254675135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.2352962448360234</v>
+        <v>2.24685124877906</v>
       </c>
       <c r="C20">
-        <v>0.1142280786453692</v>
+        <v>0.3535263922430047</v>
       </c>
       <c r="D20">
-        <v>0.006772443378851313</v>
+        <v>0.0408234011692687</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>0.2044645794326322</v>
-      </c>
-      <c r="C21">
-        <v>0.08877474521112731</v>
+          <t>Hs 852.T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D21">
-        <v>0.004444743952856234</v>
+        <v>0.1896826513059756</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22">
-        <v>1.651043442088782</v>
-      </c>
-      <c r="C22">
-        <v>0.2235260778818286</v>
+        <v>18.65771844502067</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D22">
-        <v>0.0277436840039606</v>
+        <v>0.7987754292312972</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -754,86 +762,86 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="D23">
+        <v>4.148303353180586</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>0.1286793252927361</v>
+          <t>MDA-MB-435</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>3.464392068493043</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D24">
-        <v>0.01629041722560252</v>
+        <v>0.04622180507356349</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.2359535128438055</v>
+        <v>1.018423113428254</v>
       </c>
       <c r="C25">
-        <v>0.07675091199555178</v>
+        <v>0.2016298869663588</v>
       </c>
       <c r="D25">
-        <v>0.01943777694414812</v>
+        <v>0.02296277200461775</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26">
-        <v>1.018423113428254</v>
+        <v>17.01097403910282</v>
       </c>
       <c r="C26">
-        <v>0.2016298869663588</v>
+        <v>0.2599191751404982</v>
       </c>
       <c r="D26">
-        <v>0.02296277200461775</v>
+        <v>0.2694086767088755</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.8155838226984362</v>
+        <v>0.3116999006998722</v>
       </c>
       <c r="C27">
-        <v>0.09064580900627252</v>
+        <v>0.07759798088433094</v>
       </c>
       <c r="D27">
-        <v>0.007952418224455412</v>
+        <v>0.004589298238703414</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>18.65771844502067</v>
+          <t>RPMI-7951</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -841,113 +849,111 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.7987754292312972</v>
+        <v>1.483267930410584</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>RVH-421</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>0.1903257237017469</v>
+      </c>
+      <c r="C29">
+        <v>0.08208670775185224</v>
       </c>
       <c r="D29">
-        <v>4.148303353180586</v>
+        <v>0.005570634285482893</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.5876457977663722</v>
+        <v>0.4542704531091089</v>
       </c>
       <c r="C30">
-        <v>0.1991194474043793</v>
+        <v>0.1611884269058386</v>
       </c>
       <c r="D30">
-        <v>0.0186584663117371</v>
+        <v>0.01305852878454457</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>0.3563202677326271</v>
+          <t>SK-MEL-2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C31">
-        <v>0.1415222716464925</v>
+        <v>0.09980888242691298</v>
       </c>
       <c r="D31">
-        <v>0.01763198251317507</v>
+        <v>0.0423659765280594</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.3116999006998722</v>
+        <v>0.2044645794326322</v>
       </c>
       <c r="C32">
-        <v>0.07759798088433094</v>
+        <v>0.08877474521112731</v>
       </c>
       <c r="D32">
-        <v>0.004589298238703414</v>
+        <v>0.004444743952856234</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.523623617025513</v>
+        <v>0.4425020111859396</v>
       </c>
       <c r="C33">
-        <v>0.1314457342137881</v>
+        <v>0.2239469910985226</v>
       </c>
       <c r="D33">
-        <v>0.03389691563726928</v>
+        <v>0.01811992807166913</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.1903257237017469</v>
+        <v>0.523623617025513</v>
       </c>
       <c r="C34">
-        <v>0.08208670775185224</v>
+        <v>0.1314457342137881</v>
       </c>
       <c r="D34">
-        <v>0.005570634285482893</v>
+        <v>0.03389691563726928</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -955,117 +961,111 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C35">
+        <v>0.1117205701306592</v>
       </c>
       <c r="D35">
-        <v>4.011365568566589</v>
+        <v>0.05405483045506008</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.9109394113127253</v>
-      </c>
-      <c r="C36">
-        <v>0.2804886546815576</v>
+        <v>4.29256221820035</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D36">
-        <v>0.02565810111549896</v>
+        <v>0.07344798304515984</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>4.29256221820035</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>SK23-mel</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>0.1286793252927361</v>
       </c>
       <c r="D37">
-        <v>0.07344798304515984</v>
+        <v>0.01629041722560252</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38">
-        <v>1.435263041502199</v>
+        <v>0.9109394113127253</v>
       </c>
       <c r="C38">
-        <v>0.09975869252373988</v>
+        <v>0.2804886546815576</v>
       </c>
       <c r="D38">
-        <v>0.02334934991952614</v>
+        <v>0.02565810111549896</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>UACC-62</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>0.2352962448360234</v>
+      </c>
+      <c r="C39">
+        <v>0.1142280786453692</v>
       </c>
       <c r="D39">
-        <v>0.4476872010310345</v>
+        <v>0.006772443378851313</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.6754664498443901</v>
+        <v>0.2359535128438055</v>
       </c>
       <c r="C40">
-        <v>0.1477995909589447</v>
+        <v>0.07675091199555178</v>
       </c>
       <c r="D40">
-        <v>0.02384760817354794</v>
+        <v>0.01943777694414812</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41">
-        <v>12.32461323195621</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.8155838226984362</v>
+      </c>
+      <c r="C41">
+        <v>0.09064580900627252</v>
       </c>
       <c r="D41">
-        <v>0.9904303981282423</v>
+        <v>0.007952418224455412</v>
       </c>
     </row>
   </sheetData>
@@ -1093,7 +1093,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1105,7 +1105,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1129,7 +1129,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1141,7 +1141,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1189,7 +1189,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1213,7 +1213,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1225,7 +1225,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1249,7 +1249,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1273,7 +1273,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1357,7 +1357,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1393,7 +1393,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1405,7 +1405,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1501,7 +1501,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1513,7 +1513,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1537,7 +1537,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1549,7 +1549,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
